--- a/results/auto_Cape_Town_Arts_and_Culture.xlsx
+++ b/results/auto_Cape_Town_Arts_and_Culture.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="77" uniqueCount="40">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="70" uniqueCount="40">
   <si>
     <t>Organisation Name</t>
   </si>
@@ -555,9 +555,6 @@
       <c r="D5" t="s">
         <v>27</v>
       </c>
-      <c r="G5" t="s">
-        <v>39</v>
-      </c>
     </row>
     <row r="6" spans="1:7">
       <c r="A6" t="s">
@@ -572,9 +569,6 @@
       <c r="D6" t="s">
         <v>28</v>
       </c>
-      <c r="G6" t="s">
-        <v>39</v>
-      </c>
     </row>
     <row r="7" spans="1:7">
       <c r="A7" t="s">
@@ -589,9 +583,6 @@
       <c r="D7" t="s">
         <v>29</v>
       </c>
-      <c r="G7" t="s">
-        <v>39</v>
-      </c>
     </row>
     <row r="8" spans="1:7">
       <c r="A8" t="s">
@@ -606,9 +597,6 @@
       <c r="D8" t="s">
         <v>30</v>
       </c>
-      <c r="G8" t="s">
-        <v>39</v>
-      </c>
     </row>
     <row r="9" spans="1:7">
       <c r="A9" t="s">
@@ -623,9 +611,6 @@
       <c r="D9" t="s">
         <v>31</v>
       </c>
-      <c r="G9" t="s">
-        <v>39</v>
-      </c>
     </row>
     <row r="10" spans="1:7">
       <c r="A10" t="s">
@@ -640,9 +625,6 @@
       <c r="D10" t="s">
         <v>32</v>
       </c>
-      <c r="G10" t="s">
-        <v>39</v>
-      </c>
     </row>
     <row r="11" spans="1:7">
       <c r="A11" t="s">
@@ -656,9 +638,6 @@
       </c>
       <c r="D11" t="s">
         <v>33</v>
-      </c>
-      <c r="G11" t="s">
-        <v>39</v>
       </c>
     </row>
     <row r="12" spans="1:7">

--- a/results/auto_Cape_Town_Arts_and_Culture.xlsx
+++ b/results/auto_Cape_Town_Arts_and_Culture.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="70" uniqueCount="40">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="65" uniqueCount="38">
   <si>
     <t>Organisation Name</t>
   </si>
@@ -37,21 +37,9 @@
     <t>Sent</t>
   </si>
   <si>
-    <t>Artscape Theatre Centre</t>
-  </si>
-  <si>
-    <t>Baxter Theatre Centre</t>
-  </si>
-  <si>
-    <t>Iziko Museums of South Africa</t>
-  </si>
-  <si>
     <t>Zeitz Museum of Contemporary Art Africa</t>
   </si>
   <si>
-    <t>Cape Town Philharmonic Orchestra</t>
-  </si>
-  <si>
     <t>Cape Town Opera</t>
   </si>
   <si>
@@ -82,27 +70,21 @@
     <t>Design Indaba</t>
   </si>
   <si>
+    <t>Cape Cultural Collective</t>
+  </si>
+  <si>
+    <t>District Six Museum Foundation</t>
+  </si>
+  <si>
     <t>Arts &amp; Culture</t>
   </si>
   <si>
     <t>Cape Town</t>
   </si>
   <si>
-    <t>info@artscape.co.za</t>
-  </si>
-  <si>
-    <t>info@baxter.co.za</t>
-  </si>
-  <si>
-    <t>info@iziko.org.za</t>
-  </si>
-  <si>
     <t>info@zeitzmocaa.museum</t>
   </si>
   <si>
-    <t>info@cpo.org.za</t>
-  </si>
-  <si>
     <t>info@capetownopera.co.za</t>
   </si>
   <si>
@@ -131,6 +113,18 @@
   </si>
   <si>
     <t>info@designindaba.com</t>
+  </si>
+  <si>
+    <t>info@capeculturalcollective.org</t>
+  </si>
+  <si>
+    <t>info@districtsix.co.za</t>
+  </si>
+  <si>
+    <t>021 466 7200</t>
+  </si>
+  <si>
+    <t>www.districtsix.co.za</t>
   </si>
   <si>
     <t>Yes</t>
@@ -465,7 +459,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G16"/>
+  <dimension ref="A1:G14"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:7">
@@ -496,16 +490,16 @@
         <v>7</v>
       </c>
       <c r="B2" t="s">
+        <v>20</v>
+      </c>
+      <c r="C2" t="s">
+        <v>21</v>
+      </c>
+      <c r="D2" t="s">
         <v>22</v>
       </c>
-      <c r="C2" t="s">
-        <v>23</v>
-      </c>
-      <c r="D2" t="s">
-        <v>24</v>
-      </c>
       <c r="G2" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -513,16 +507,16 @@
         <v>8</v>
       </c>
       <c r="B3" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="C3" t="s">
+        <v>21</v>
+      </c>
+      <c r="D3" t="s">
         <v>23</v>
       </c>
-      <c r="D3" t="s">
-        <v>25</v>
-      </c>
       <c r="G3" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -530,16 +524,16 @@
         <v>9</v>
       </c>
       <c r="B4" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="C4" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="D4" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="G4" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
     </row>
     <row r="5" spans="1:7">
@@ -547,13 +541,16 @@
         <v>10</v>
       </c>
       <c r="B5" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="C5" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="D5" t="s">
-        <v>27</v>
+        <v>25</v>
+      </c>
+      <c r="G5" t="s">
+        <v>37</v>
       </c>
     </row>
     <row r="6" spans="1:7">
@@ -561,13 +558,13 @@
         <v>11</v>
       </c>
       <c r="B6" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="C6" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="D6" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
     </row>
     <row r="7" spans="1:7">
@@ -575,13 +572,13 @@
         <v>12</v>
       </c>
       <c r="B7" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="C7" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="D7" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
     </row>
     <row r="8" spans="1:7">
@@ -589,13 +586,13 @@
         <v>13</v>
       </c>
       <c r="B8" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="C8" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="D8" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
     </row>
     <row r="9" spans="1:7">
@@ -603,13 +600,13 @@
         <v>14</v>
       </c>
       <c r="B9" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="C9" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="D9" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
     </row>
     <row r="10" spans="1:7">
@@ -617,13 +614,13 @@
         <v>15</v>
       </c>
       <c r="B10" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="C10" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="D10" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
     </row>
     <row r="11" spans="1:7">
@@ -631,13 +628,13 @@
         <v>16</v>
       </c>
       <c r="B11" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="C11" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="D11" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
     </row>
     <row r="12" spans="1:7">
@@ -645,13 +642,13 @@
         <v>17</v>
       </c>
       <c r="B12" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="C12" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="D12" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
     </row>
     <row r="13" spans="1:7">
@@ -659,13 +656,13 @@
         <v>18</v>
       </c>
       <c r="B13" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="C13" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="D13" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
     </row>
     <row r="14" spans="1:7">
@@ -673,41 +670,19 @@
         <v>19</v>
       </c>
       <c r="B14" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="C14" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="D14" t="s">
+        <v>34</v>
+      </c>
+      <c r="E14" t="s">
+        <v>35</v>
+      </c>
+      <c r="F14" t="s">
         <v>36</v>
-      </c>
-    </row>
-    <row r="15" spans="1:7">
-      <c r="A15" t="s">
-        <v>20</v>
-      </c>
-      <c r="B15" t="s">
-        <v>22</v>
-      </c>
-      <c r="C15" t="s">
-        <v>23</v>
-      </c>
-      <c r="D15" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="16" spans="1:7">
-      <c r="A16" t="s">
-        <v>21</v>
-      </c>
-      <c r="B16" t="s">
-        <v>22</v>
-      </c>
-      <c r="C16" t="s">
-        <v>23</v>
-      </c>
-      <c r="D16" t="s">
-        <v>38</v>
       </c>
     </row>
   </sheetData>

--- a/results/auto_Cape_Town_Arts_and_Culture.xlsx
+++ b/results/auto_Cape_Town_Arts_and_Culture.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="65" uniqueCount="38">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="66" uniqueCount="38">
   <si>
     <t>Organisation Name</t>
   </si>
@@ -566,6 +566,9 @@
       <c r="D6" t="s">
         <v>26</v>
       </c>
+      <c r="G6" t="s">
+        <v>37</v>
+      </c>
     </row>
     <row r="7" spans="1:7">
       <c r="A7" t="s">
